--- a/relatorios/dados_site.xlsx
+++ b/relatorios/dados_site.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-08 12:55:15</t>
+          <t>2026-08-09 11:14:16</t>
         </is>
       </c>
     </row>
@@ -505,22 +505,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>331926</t>
+          <t>333022</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>331927</t>
+          <t>333023</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>332728</t>
+          <t>333296</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-08 16:36:11</t>
+          <t>2026-08-09 11:16:43</t>
         </is>
       </c>
     </row>
